--- a/AAII_Financials/Quarterly/EOG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EOG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>EOG</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8522000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6777000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5673000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5749000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5371000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5861000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5673000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5893000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6052000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5860000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6059000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6134000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5481000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5599000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6746000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7614000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7310000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3958000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6073000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4764000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4088000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3700000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2971100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2316500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1090100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4701200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4200300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4304000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4689600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4062500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4494600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4665700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4244400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3696100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3405700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2653000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2621400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2627300</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2298000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2010300</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3093000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2520000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2219000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2152000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2067000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2166000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2158000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2337000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2303000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2213000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2310000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2158000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2200000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2115000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2258000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2380000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2852000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1978000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1865000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1822000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1608000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1455000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1203700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1044900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>945100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1782600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1915600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2024300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2141400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1900700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2010900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1964400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2027700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1691700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1533400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1266300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1272200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1215400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1107300</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1016400</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5429000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4257000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3454000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3597000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3304000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3695000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3515000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3556000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3749000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3647000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3749000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3976000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3281000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3484000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4488000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5234000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4458000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1980000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4208000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2942000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2480000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2245000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1767400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1271600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>145000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2918600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2284700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2279700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2548200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2161800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2483700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2701300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2216700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2004400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1872300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1386700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1349200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1411900</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1190700</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>993900</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1279,86 +1293,89 @@
       <c r="P12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R12" s="3">
         <v>43000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>53000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>50000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>43000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>80000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>44000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>43000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>38000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>34400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>50000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>20600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>32800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>28600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>53500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>29800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>29900</v>
-      </c>
-      <c r="AG12" s="3">
-        <v>27400</v>
       </c>
       <c r="AH12" s="3">
         <v>27400</v>
       </c>
       <c r="AI12" s="3">
+        <v>27400</v>
+      </c>
+      <c r="AJ12" s="3">
         <v>46700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>27900</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>20600</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>26100</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>29400</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>50700</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>33900</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,252 +1496,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-58000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-31000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>18000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>74000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>14000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>24000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>10000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-26000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>33000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-35000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-69000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>142000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>94000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>91000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>55000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>206000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>82000</v>
-      </c>
-      <c r="W14" s="3">
-        <v>44000</v>
       </c>
       <c r="X14" s="3">
         <v>44000</v>
       </c>
       <c r="Y14" s="3">
+        <v>44000</v>
+      </c>
+      <c r="Z14" s="3">
         <v>142400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>79000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>305400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1572900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>228100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>105300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>112100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>72400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>186100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>44600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>51700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>64600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>153400</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>53700</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>78900</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>193200</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>297900</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>178000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1278000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1212000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1913000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1184000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1077000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1057000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1293000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1046000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1034000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1093000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>978000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>951000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>900000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>832000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>878000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>906000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>911000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>847000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>910000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>927000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>914000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>900000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>870600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>823100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>706700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1000100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>959200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>953600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>957300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>879600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>920000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>918200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>848700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>748600</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>881700</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>846200</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>865400</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>816000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>862500</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>899500</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>5052000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4210000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4712000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3839000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3609000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4001000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4056000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3797000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3911000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3615000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3524000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3611000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3501000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3096000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3893000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3950000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4407000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3412000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3545000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3293000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2917000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2768000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2483400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2319200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2176700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4643600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3336500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3476000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3558900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3185900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3371500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3159000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3279500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2821500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2929700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2438200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2493500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2519600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2403500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2203800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3470000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2567000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>961000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1910000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1762000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1860000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1617000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2096000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2141000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2245000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2535000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2523000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1980000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2503000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2853000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3664000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2903000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>546000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2528000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1471000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1171000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>932000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>487700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1086600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>57600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>863800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>828000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1130800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>876600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1123100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1506700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>964900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>874600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>476000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>214800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>127900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>107700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-105500</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>-193500</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E20" s="3">
         <v>8000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3000</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-62000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>172000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-51000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-50000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-65000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>48000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>40000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>27000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>9000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>6000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>18100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>8100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>9100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>8500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>5600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>21300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>3300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-8600</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>800</v>
       </c>
       <c r="AK20" s="3">
         <v>800</v>
       </c>
       <c r="AL20" s="3">
+        <v>800</v>
+      </c>
+      <c r="AM20" s="3">
         <v>300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>5000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>3200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-17200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-7900</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>4751000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3771000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2878000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3096000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2837000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2914000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2910000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3142000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3176000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3400000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3341000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3525000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2930000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3400000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3779000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4610000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3841000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1392000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3447000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2404000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2083000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1828000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1351400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>823700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-384400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1075800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1831100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1790700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2096600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1761700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2064300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2428200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1805100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1623900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1358500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1061300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>998300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>926900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>739800</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>698100</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>66000</v>
+        <v>67000</v>
       </c>
       <c r="E22" s="3">
         <v>66000</v>
       </c>
       <c r="F22" s="3">
+        <v>66000</v>
+      </c>
+      <c r="G22" s="3">
         <v>71000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>51000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>47000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>38000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>31000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>36000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>33000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>35000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>36000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>35000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>42000</v>
       </c>
       <c r="Q22" s="3">
         <v>42000</v>
       </c>
       <c r="R22" s="3">
+        <v>42000</v>
+      </c>
+      <c r="S22" s="3">
         <v>41000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>48000</v>
       </c>
       <c r="T22" s="3">
         <v>48000</v>
       </c>
       <c r="U22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="V22" s="3">
         <v>38000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>48000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>45000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>47000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>53100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>53200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>54200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>44700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>40700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>39600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>49900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>54900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>56000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>63600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>63400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>62000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>63400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>69100</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>70400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>71500</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>71300</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>70900</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>3499000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2555000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>910000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1824000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1751000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1877000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1624000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2134000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2160000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2300000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2535000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2573000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1986000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2595000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2859000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3663000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2882000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>497000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2499000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1429000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1124000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>881000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>427800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-52600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1145300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>31000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>831200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>797500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1089400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>827200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1088300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1446400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>892900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>813400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>413400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>146000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>62500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>39400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-194000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-272300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>775000</v>
+      </c>
+      <c r="E24" s="3">
         <v>575000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>209000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>353000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>406000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>414000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>373000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>461000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>470000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>511000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>547000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>543000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>433000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>572000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>582000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>809000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>644000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>107000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>514000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>334000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>217000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>204000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>90300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-235900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>21200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>194700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>182300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>241500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>191800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>195600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>307400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>196200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>174800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>182900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>45400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>39400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>10900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-51700</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-82300</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>2724000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1980000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>701000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1471000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1345000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1463000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1251000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1673000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1690000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1789000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1988000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2030000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1553000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2023000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2277000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2854000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2238000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>390000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1985000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1095000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>907000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>677000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>337500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-42500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-909400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>9800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>636500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>615100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>847800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>635400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>892800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1139000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>696700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>638600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>230500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>100500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>23100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>28500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-142400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-190000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>2724000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1980000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>701000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1471000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1345000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1463000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1251000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1673000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1690000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1789000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1988000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2030000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1553000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2023000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2277000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2854000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2238000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>390000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1985000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1095000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>907000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>677000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>337500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-42500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-909400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>9800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>636500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>615100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>847800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>635400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>892800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1139000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>696700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>638600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>230500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>100500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>23100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>28500</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-142400</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-190000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3227,8 +3288,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>24</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>24</v>
@@ -3242,23 +3303,23 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>52000</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL29" s="3">
         <v>2200000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3000</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>62000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-172000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>51000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>50000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>65000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-48000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-40000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-27000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-9000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-6000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>4500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-8100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-9100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-8500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-21300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>8600</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>-800</v>
       </c>
       <c r="AK32" s="3">
         <v>-800</v>
       </c>
       <c r="AL32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AM32" s="3">
         <v>-300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>17200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2724000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1980000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>701000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1471000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1345000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1463000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1251000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1673000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1690000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1789000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1988000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2030000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1553000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2023000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2277000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2854000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2238000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>390000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1985000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1095000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>907000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>677000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>337500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-42500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-909400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>9800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>636500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>615100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>847800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>635400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>892800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1191000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>696700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>638600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2430500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>100500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>23100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>28500</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-142400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-190000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2724000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1980000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>701000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1471000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1345000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1463000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1251000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1673000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1690000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1789000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1988000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2030000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1553000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2023000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2277000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2854000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2238000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>390000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1985000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1095000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>907000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>677000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>337500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-42500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-909400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>9800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>636500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>615100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>847800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>635400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>892800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1191000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>696700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>638600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2430500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>100500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>23100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>28500</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-142400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-190000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4907000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3849000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3396000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3530000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5216000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6599000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7092000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6122000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5431000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5292000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5278000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5326000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4764000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5018000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5972000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5272000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3073000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4009000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5209000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4293000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3880000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3388000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3328900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3065600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2416500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2906900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2028000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1583100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1160500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1135800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1555600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1274100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1008200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>816100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>834200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>846100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1649400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1546600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1599900</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1048700</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,496 +4553,511 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3529000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3597000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2681000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2680000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2504000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2621000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2650000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2547000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2659000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2688000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2716000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2927000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2264000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2455000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2871000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3436000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3735000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3213000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2335000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2154000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2026000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1828000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1545300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1137500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1140300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1759000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2153300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2063700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2123300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2643700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2343100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2472200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2272100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1964900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1710900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1370400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1205700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1267600</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1228600</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>920400</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>930000</v>
+      </c>
+      <c r="E44" s="3">
         <v>955000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1014000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>945000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>934000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>897000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>985000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1038000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1069000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1154000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1275000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1379000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1355000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1131000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1058000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>872000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>739000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>586000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>584000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>521000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>516000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>562000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>629400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>668500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>676600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>662400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>767300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>778100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>853100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>860800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>859400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>767000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>671000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>584700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>483900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>344000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>336200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>314200</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>350000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>429700</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>511000</v>
+      </c>
+      <c r="E45" s="3">
         <v>562000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>565000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>665000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>591000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>563000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>503000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>458000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>644000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>794000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>666000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>626000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>523000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>580000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>574000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>621000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>606000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>671000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>456000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>381000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>513000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>413000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>358500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>223400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>364000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1162800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>324700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>394800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>358600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>267700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>299300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>303800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>280500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>219400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>250200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>203400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>192000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>265700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>376100</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>339000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9877000</v>
+      </c>
+      <c r="E46" s="3">
         <v>8963000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7656000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7820000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9245000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10680000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11230000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10165000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9803000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9928000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9935000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10258000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8906000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9184000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10475000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>10201000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8153000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8479000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8584000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7349000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6935000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6191000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5862200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5095100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4597400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6491000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5273300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4819700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4495500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4907900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5057400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4817100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4231900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3585100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3279100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2764000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3383400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>3394100</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>3385200</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2737800</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4995,8 +5100,8 @@
       <c r="P47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5073,130 +5178,136 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>43240000</v>
+      </c>
+      <c r="E48" s="3">
         <v>42674000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>43517000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>42585000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>35361000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34632000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>35217000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34126000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33644000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33077000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>33271000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>31723000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>30910000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>30223000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>30275000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>29101000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>28847000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>28462000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>29169000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>28545000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>28659000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>28666000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>29467600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>28633000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>29233500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>29694100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>31137600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>31046300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>30619400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>30029000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>28075500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>27947700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>27153800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>26375600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>25665000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>25724600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>25580200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>25606500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>25707100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>22644400</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5317,8 +5428,11 @@
       <c r="AP49" s="3">
         <v>0</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1631000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1711000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>587000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1757000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1639000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1626000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>700000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1818000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1733000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1753000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>609000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1633000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1638000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1587000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>621000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1185000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1139000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1156000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>483000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1278000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1291000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1314000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>474800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1346000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1390800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1449000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>713700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>676200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>636500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>726600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>801600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>872900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>706700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>779800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>888900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>316800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>300100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>211400</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>206900</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>172800</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>54783000</v>
+      </c>
+      <c r="E54" s="3">
         <v>53378000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>51799000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>52199000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>46284000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>46982000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>47186000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>46151000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>45224000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>44796000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>43857000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>43647000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>41487000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>41025000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>41371000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>40487000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>38139000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>38097000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>38236000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>37172000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>36885000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>36171000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>35804600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>35074000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>35221700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>37634100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>37124600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>36542300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>35751500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>35663500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>33934500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>33637700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>32092400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>30740500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>29833100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>28805300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>29263600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>29212000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>29299200</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>25554900</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,243 +6145,247 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3374000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3186000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2904000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2944000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2266000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2353000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2464000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2290000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2436000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2389000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2437000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2464000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2205000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2438000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2532000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2718000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2896000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2660000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2242000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1972000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2012000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1945000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1681200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1245000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1281200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2892300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2429100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2395100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2387400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2452300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2239900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2435800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2337000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1915700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1847100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1635700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1615200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1556900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1511800</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1296200</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>351000</v>
+      </c>
+      <c r="E58" s="3">
         <v>402000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>499000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>460000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1138000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1598000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>847000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>372000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>837000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>352000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>359000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>371000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>369000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>387000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1283000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>1282000</v>
       </c>
       <c r="S58" s="3">
         <v>1282000</v>
       </c>
       <c r="T58" s="3">
+        <v>1282000</v>
+      </c>
+      <c r="U58" s="3">
         <v>1283000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>37000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>38000</v>
-      </c>
-      <c r="W58" s="3">
-        <v>39000</v>
       </c>
       <c r="X58" s="3">
         <v>39000</v>
       </c>
       <c r="Y58" s="3">
+        <v>39000</v>
+      </c>
+      <c r="Z58" s="3">
         <v>781100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>770800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>21100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>519000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1014500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1014200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1013900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>914900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>913100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1262900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1262500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>363200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>356200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>6600</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>606500</v>
-      </c>
-      <c r="AN58" s="3">
-        <v>6600</v>
       </c>
       <c r="AO58" s="3">
         <v>6600</v>
@@ -6259,496 +6393,511 @@
       <c r="AP58" s="3">
         <v>6600</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>6600</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1610000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1636000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1288000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1411000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1771000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1768000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2043000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1744000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1355000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1532000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1278000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1390000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1157000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1403000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1698000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1746000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1590000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2321000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1763000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1474000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1951000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1328000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>997900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1004200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>852100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>893700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1043300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1064400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1012800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>934100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>575400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>726500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>697800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>558000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>522200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>537700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>500600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>468600</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>508900</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>430100</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5335000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5224000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4691000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4815000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5175000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5719000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5354000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4406000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4628000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4273000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4074000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4225000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3731000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4228000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5513000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5746000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5768000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6264000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4042000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3484000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4002000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3312000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3460100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3020000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2154400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4305000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4487000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4473700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4414100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4301300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3728400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4425100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4297300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2836800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2725500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2180000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2722300</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2032000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2027300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1733000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7899000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7904000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8636000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7667000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3458000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3464000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4945000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3742000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3250000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3757000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4441000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3772000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3780000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3787000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3795000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3802000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3809000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3816000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5072000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5079000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5086000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5094000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5035400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4949900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5703100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4703200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4160900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4163100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4165300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5166100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5170200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5171900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5172300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6071600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6030800</v>
-      </c>
-      <c r="AL61" s="3">
-        <v>6380400</v>
       </c>
       <c r="AM61" s="3">
         <v>6380400</v>
       </c>
       <c r="AN61" s="3">
+        <v>6380400</v>
+      </c>
+      <c r="AO61" s="3">
         <v>6980000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>6979800</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>6979500</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2468000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2476000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1785000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2496000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2398000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2368000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1670000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2480000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2456000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2533000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1850000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2698000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2581000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2620000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7284000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7090000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6250000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6477000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6942000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6844000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6916000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7003000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7007300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6955700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6976600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7155200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6836000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6781200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6541900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6292400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5671800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5502200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5170400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4991500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>4793400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>6322600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>6259300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>6271700</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>6310600</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>5044100</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22919000</v>
+      </c>
+      <c r="E66" s="3">
         <v>22470000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>21966000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>21914000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17046000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17466000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17835000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16577000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16065000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16160000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15767000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15889000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15230000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15578000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16592000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16638000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15827000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>16557000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16056000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15407000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16004000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15409000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15502700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14925700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>14834100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16163400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15483900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>15418000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>15121200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>15759700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>14570300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>15099300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>14640000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13899900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>13549800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>14883000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>15361900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>15283700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>15317600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>13756600</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>33390000</v>
+      </c>
+      <c r="E72" s="3">
         <v>31200000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>29765000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>29603000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>28131000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>27869000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>26941000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>26231000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>25071000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>23897000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>22634000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>22047000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20497000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>19423000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18472000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17563000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>16028000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15283000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15919000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15542000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14689000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14606000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>14170000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>14051200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>14312500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>15440100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>15648600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>15179400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>14731600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>14050700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13543100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>12778100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>11714700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>11125100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>10593500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>8260000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>8256400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>8330000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>8398100</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>8641700</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>31864000</v>
+      </c>
+      <c r="E76" s="3">
         <v>30908000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>29833000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>30285000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>29238000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>29516000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>29351000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>29574000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>29159000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>28636000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>28090000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>27758000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>26257000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>25447000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>24779000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>23849000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>22312000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>21540000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>22180000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21765000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>20881000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>20762000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>20301900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>20148300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>20387600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>21470700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>21640700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>21124300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20630300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>19903800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>19364200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>18538500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>17452400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>16840600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>16283300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>13922300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>13901700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>13928200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>13981600</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>11798300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2724000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1980000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>701000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1471000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1345000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1463000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1251000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1673000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1690000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1789000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1988000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2030000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1553000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2023000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2277000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2854000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2238000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>390000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1985000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1095000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>907000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>677000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>337500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-42500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-909400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>9800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>636500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>615100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>847800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>635400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>892800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1191000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>696700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>638600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2430500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>100500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>23100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>28500</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-142400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-190000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1053000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1013000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1019000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1031000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>984000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1074000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>930000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>898000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>866000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>798000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>878000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>906000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>911000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>847000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>878000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>906000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>911000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>847000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>910000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>927000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>914000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>900000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>870600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>823100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>706700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1000100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>959200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>953600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>957300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>879600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>920000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>918200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>848700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>748600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>881700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>846200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>865400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>816000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>862500</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>899500</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4669000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2966000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2612000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3111000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2032000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2289000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2763000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3588000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2889000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2903000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3104000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2704000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2277000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3255000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3444000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4773000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2048000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>828000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3166000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2196000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1559000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1870000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1121200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1213600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>88100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2584900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1807200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2061700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2686500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1607800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2085200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2189600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1941600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1552200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1327500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>961400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1078400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>898000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>804700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>759600</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1782000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1644000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1655000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1663000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1793000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1483000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1365000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1502000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1670000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1835000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1522000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1518000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1521000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1624000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1362000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1205000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1424000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1014000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-896000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-55000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-42000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-56200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-17700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-24600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-122800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-83300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-70500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-55900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-61000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-34800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-57500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-68800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-76100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-33800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-51500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-53700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-946600</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-740900</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-653800</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1781000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1545000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1762000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5963000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1781000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1430000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1276000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1561000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1533000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1597000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1499000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1532000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1742000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1567000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1397000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1216000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1487000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-956000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-837000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-933000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-828000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-821000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-636800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-334500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-845200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1530900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1456500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1632700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1891000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1291900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1788700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1633200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1456400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1231900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1036400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-882700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-836400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>10700</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-382500</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>540000</v>
+      </c>
+      <c r="E96" s="3">
         <v>544000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>550000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>545000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>528000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>538000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>509000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>533000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>520000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>525000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>1929700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>757000</v>
       </c>
-      <c r="O96" s="3" t="s">
+      <c r="P96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>1067000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1327000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1312000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1486000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1023000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1406000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-820000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-239000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-219000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-219600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-217100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-217000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-167100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-167300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-166200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-127100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-127500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-127000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-107500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-106600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-97000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-97300</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>-96300</v>
       </c>
       <c r="AM96" s="3">
         <v>-96300</v>
       </c>
       <c r="AN96" s="3">
+        <v>-96300</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-96700</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-96100</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-92700</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,141 +10953,147 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1830000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-968000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-984000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1167000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1635000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1352000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-516000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1336000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1217000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1292000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1653000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-610000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-789000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2642000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1347000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1357000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1497000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1072000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1414000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-850000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-241000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-988000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-219500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-231800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>267500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-175300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-165100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-182500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1029100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-136600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-476600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-134700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-113900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-114000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-102300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-725100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-93700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-114600</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-270900</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-108100</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>24</v>
@@ -10864,216 +11113,222 @@
       <c r="L101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>-100</v>
       </c>
       <c r="AE101" s="3">
         <v>-100</v>
       </c>
       <c r="AF101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-35300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-3100</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-400</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>6600</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1058000</v>
+      </c>
+      <c r="E102" s="3">
         <v>453000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-134000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1685000</v>
       </c>
-      <c r="G102" s="3">
-        <v>-1384000</v>
-      </c>
       <c r="H102" s="3">
+        <v>-1383000</v>
+      </c>
+      <c r="I102" s="3">
         <v>-493000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>970000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>691000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>139000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>14000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-48000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>562000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-254000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-954000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>700000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2199000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-936000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1200000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>916000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>413000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>492000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>59000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>263400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>649100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-490400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>878900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>444900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>422600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>24700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-419800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>281500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>265900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>192100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-18100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-11900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-803300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>102900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-53300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>551200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>269000</v>
       </c>
     </row>
